--- a/CiviFix_Selenium_Execution_Report.xlsx
+++ b/CiviFix_Selenium_Execution_Report.xlsx
@@ -49,7 +49,7 @@
       <color rgb="00A9B0B7"/>
     </font>
     <font>
-      <color rgb="003BBA9C"/>
+      <color rgb="005D9CEC"/>
     </font>
     <font>
       <b val="1"/>
@@ -505,8 +505,8 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Execution Time: 07/23/2026, 04:32:22 PM | Environment: QA-Selenium | Overall Status: PASS</t>
+          <t>Execution Time: 07/23/2026, 05:04:39 PM | Environment: QA-Selenium | Overall Status: PASS</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>test_verify_gps_location</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr"/>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>3.2</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="13">
@@ -725,12 +725,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_validate_street_light_issue</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="H13" s="11" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="14">
@@ -756,7 +756,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>4.79</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -787,12 +787,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="H15" s="11" t="n">
-        <v>11.32</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="16">
@@ -823,7 +823,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>test_update_password_reset</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr"/>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>7.58</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="17">
@@ -849,12 +849,12 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_verify_pothole_complaint</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="H17" s="11" t="n">
-        <v>10.62</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="18">
@@ -880,12 +880,12 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>test_submit_street_light_issue</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr"/>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>7.99</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="19">
@@ -911,12 +911,12 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>test_verify_pothole_complaint</t>
+          <t>test_refresh_street_light_issue</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H19" s="11" t="n">
-        <v>10.62</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="20">
@@ -942,12 +942,12 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr"/>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>10.02</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="21">
@@ -973,12 +973,12 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>test_update_password_reset</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="H21" s="11" t="n">
-        <v>3.31</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="22">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>test_submit_user_profile</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>11.6</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="23">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="H23" s="11" t="n">
-        <v>7.19</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="24">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>test_create_pothole_complaint</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>4.07</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="25">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H25" s="11" t="n">
-        <v>4.84</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="26">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>8.76</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="27">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_submit_gps_location</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H27" s="11" t="n">
-        <v>3.77</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="28">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_validate_login_credentials</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>9.960000000000001</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="29">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>test_create_pothole_complaint</t>
+          <t>test_verify_password_reset</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="H29" s="11" t="n">
-        <v>2.79</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="30">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>test_validate_street_light_issue</t>
+          <t>test_validate_user_profile</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>5.92</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="31">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>test_verify_admin_dashboard</t>
+          <t>test_verify_resolution_status</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="H31" s="11" t="n">
-        <v>8.470000000000001</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="32">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>12.27</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="33">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>test_create_pothole_complaint</t>
+          <t>test_verify_admin_dashboard</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr"/>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H33" s="11" t="n">
-        <v>11.65</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="34">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>test_verify_street_light_issue</t>
+          <t>test_verify_resolution_status</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>12.09</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="35">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_refresh_password_reset</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="H35" s="11" t="n">
-        <v>4.26</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="36">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>test_validate_admin_dashboard</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>5.93</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="H37" s="11" t="n">
-        <v>9.92</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="38">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>2.89</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="39">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_delete_admin_dashboard</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="H39" s="11" t="n">
-        <v>5.71</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="40">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>9.01</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="41">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>test_delete_street_light_issue</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr"/>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="H41" s="11" t="n">
-        <v>12.36</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="42">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>test_create_gps_location</t>
+          <t>test_validate_admin_dashboard</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr"/>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>9.449999999999999</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="43">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>test_update_gps_location</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="H43" s="11" t="n">
-        <v>5.38</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="44">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_validate_resolution_status</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>7.16</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>test_update_resolution_status</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="H45" s="11" t="n">
-        <v>11.29</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="46">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>test_validate_admin_dashboard</t>
+          <t>test_delete_user_profile</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>9.369999999999999</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="47">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>test_verify_image_upload</t>
+          <t>test_submit_gps_location</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="H47" s="11" t="n">
-        <v>6.48</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="48">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>7.94</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="49">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="H49" s="11" t="n">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="50">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>test_delete_login_credentials</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr"/>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>2.72</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="51">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_validate_street_light_issue</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="H51" s="11" t="n">
-        <v>6.62</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="52">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>test_validate_pothole_complaint</t>
+          <t>test_refresh_resolution_status</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr"/>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>3.38</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="53">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_update_pothole_complaint</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H53" s="11" t="n">
-        <v>7.68</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="54">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_verify_resolution_status</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>6.34</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="55">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>test_create_image_upload</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="H55" s="11" t="n">
-        <v>5.75</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="56">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>test_verify_admin_dashboard</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>3.47</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="57">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="H57" s="11" t="n">
-        <v>2.72</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="58">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_refresh_user_profile</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>10.92</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="59">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="H59" s="11" t="n">
-        <v>3.14</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="60">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>11.9</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="61">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H61" s="11" t="n">
-        <v>2.64</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="62">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>test_validate_pothole_complaint</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>8.970000000000001</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="63">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>test_create_admin_dashboard</t>
+          <t>test_validate_resolution_status</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="H63" s="11" t="n">
-        <v>7.94</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="64">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr"/>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>6.3</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="65">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>test_submit_street_light_issue</t>
+          <t>test_delete_admin_dashboard</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr"/>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="H65" s="11" t="n">
-        <v>9.99</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="66">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_validate_gps_location</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr"/>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>8.380000000000001</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>test_validate_gps_location</t>
+          <t>test_refresh_password_reset</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="H67" s="11" t="n">
-        <v>4.83</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>test_update_gps_location</t>
+          <t>test_validate_gps_location</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>2.78</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="69">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>test_verify_admin_dashboard</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="H69" s="11" t="n">
-        <v>6.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="70">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>11.79</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="71">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>test_verify_gps_location</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="H71" s="11" t="n">
-        <v>9.970000000000001</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="72">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_gps_location</t>
+          <t>test_verify_pothole_complaint</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>7.93</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="73">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_gps_location</t>
+          <t>test_validate_admin_dashboard</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="H73" s="11" t="n">
-        <v>7.53</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="74">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>9.300000000000001</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="75">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>test_submit_admin_dashboard</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr"/>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="H75" s="11" t="n">
-        <v>8.699999999999999</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="76">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>test_update_resolution_status</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>7.68</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>test_create_admin_dashboard</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="H77" s="11" t="n">
-        <v>4.56</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="78">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_user_profile</t>
+          <t>test_refresh_street_light_issue</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>12.18</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="79">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_user_profile</t>
+          <t>test_submit_gps_location</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="H79" s="11" t="n">
-        <v>3.92</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="80">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>11.83</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="81">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>test_verify_image_upload</t>
+          <t>test_validate_gps_location</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr"/>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="H81" s="11" t="n">
-        <v>7.28</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="82">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>test_create_gps_location</t>
+          <t>test_verify_pothole_complaint</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>5.66</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="83">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>test_submit_admin_dashboard</t>
+          <t>test_refresh_admin_dashboard</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="H83" s="11" t="n">
-        <v>10.25</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="84">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>test_submit_user_profile</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>3.37</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="85">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr"/>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="H85" s="11" t="n">
-        <v>3.78</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="86">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>9.539999999999999</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="87">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_refresh_user_profile</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H87" s="11" t="n">
-        <v>5.24</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="88">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>test_delete_pothole_complaint</t>
+          <t>test_submit_password_reset</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="89">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>test_update_login_credentials</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="H89" s="11" t="n">
-        <v>7.85</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>4.86</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="91">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="H91" s="11" t="n">
-        <v>10.67</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="92">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>11.85</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="93">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>test_delete_login_credentials</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="H93" s="11" t="n">
-        <v>3.26</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="94">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr"/>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>7.51</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="95">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="H95" s="11" t="n">
-        <v>3.93</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="96">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_create_image_upload</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>6.33</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="97">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>test_verify_admin_dashboard</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr"/>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="H97" s="11" t="n">
-        <v>6.51</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="98">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>test_verify_password_reset</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="H98" s="11" t="n">
-        <v>5.92</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="99">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="H99" s="11" t="n">
-        <v>5.33</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="100">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_verify_password_reset</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="H100" s="11" t="n">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="101">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>test_submit_street_light_issue</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr"/>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="H101" s="11" t="n">
-        <v>3.06</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="102">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr"/>
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="H102" s="11" t="n">
-        <v>11.51</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="103">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="H103" s="11" t="n">
-        <v>5.11</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="104">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>test_delete_street_light_issue</t>
+          <t>test_validate_pothole_complaint</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="H104" s="11" t="n">
-        <v>3.51</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="105">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>test_verify_resolution_status</t>
+          <t>test_refresh_gps_location</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr"/>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="H105" s="11" t="n">
-        <v>12.02</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="106">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>test_delete_user_profile</t>
+          <t>test_create_user_profile</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr"/>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="H106" s="11" t="n">
-        <v>9.359999999999999</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="107">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_verify_resolution_status</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr"/>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="H107" s="11" t="n">
-        <v>9.67</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="108">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>test_update_login_credentials</t>
+          <t>test_verify_user_profile</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="H108" s="11" t="n">
-        <v>7.02</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="109">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>test_submit_gps_location</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr"/>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="H109" s="11" t="n">
-        <v>6.96</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="110">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>test_delete_admin_dashboard</t>
+          <t>test_create_gps_location</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="H110" s="11" t="n">
-        <v>6.15</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="111">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="H111" s="11" t="n">
-        <v>4.03</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="112">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_admin_dashboard</t>
+          <t>test_validate_image_upload</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr"/>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="H112" s="11" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="H113" s="11" t="n">
-        <v>9.59</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="114">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>test_validate_login_credentials</t>
+          <t>test_refresh_admin_dashboard</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="H114" s="11" t="n">
-        <v>10.56</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="115">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="H115" s="11" t="n">
-        <v>6.64</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="116">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>test_verify_gps_location</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="H116" s="11" t="n">
-        <v>2.88</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="117">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>test_create_login_credentials</t>
+          <t>test_submit_pothole_complaint</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr"/>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="H117" s="11" t="n">
-        <v>4.44</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="118">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr"/>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="H118" s="11" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="119">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr"/>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="H119" s="11" t="n">
-        <v>11.43</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="120">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>test_verify_gps_location</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="H120" s="11" t="n">
-        <v>3.63</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="121">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>test_validate_gps_location</t>
+          <t>test_delete_password_reset</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="H121" s="11" t="n">
-        <v>9.1</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="122">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr"/>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="H122" s="11" t="n">
-        <v>10.99</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="123">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_validate_login_credentials</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="H123" s="11" t="n">
-        <v>9.65</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="124">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>test_validate_login_credentials</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="H124" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="125">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="H125" s="11" t="n">
-        <v>12.08</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_verify_pothole_complaint</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="H126" s="11" t="n">
-        <v>2.92</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="127">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>test_update_login_credentials</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H127" s="11" t="n">
-        <v>9.869999999999999</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="128">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="H128" s="11" t="n">
-        <v>8.84</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="129">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr"/>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="H129" s="11" t="n">
-        <v>5.47</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="130">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_resolution_status</t>
+          <t>test_create_login_credentials</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr"/>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="H130" s="11" t="n">
-        <v>5.95</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="131">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_admin_dashboard</t>
+          <t>test_refresh_resolution_status</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr"/>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="H131" s="11" t="n">
-        <v>2.77</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="132">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_create_pothole_complaint</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="H132" s="11" t="n">
-        <v>7.95</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="133">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr"/>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="H133" s="11" t="n">
-        <v>8.59</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="134">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr"/>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="H134" s="11" t="n">
-        <v>5.85</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_update_password_reset</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr"/>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="H135" s="11" t="n">
-        <v>3.42</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="136">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>test_submit_user_profile</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="H136" s="11" t="n">
-        <v>12.43</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="137">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>test_validate_pothole_complaint</t>
+          <t>test_verify_password_reset</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="H137" s="11" t="n">
-        <v>7.63</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="138">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr"/>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="H138" s="11" t="n">
-        <v>7.54</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="139">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>test_verify_street_light_issue</t>
+          <t>test_update_street_light_issue</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="H139" s="11" t="n">
-        <v>4.63</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="140">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>test_update_password_reset</t>
+          <t>test_refresh_gps_location</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="H140" s="11" t="n">
-        <v>6.87</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="141">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_password_reset</t>
+          <t>test_submit_image_upload</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr"/>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="H141" s="11" t="n">
-        <v>6.3</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="142">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr"/>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="H142" s="11" t="n">
-        <v>11.44</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="143">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_submit_gps_location</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="H143" s="11" t="n">
-        <v>10.34</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="144">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>test_validate_gps_location</t>
+          <t>test_refresh_street_light_issue</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="H144" s="11" t="n">
-        <v>9</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="145">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_validate_user_profile</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="H145" s="11" t="n">
-        <v>11.24</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="146">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="H146" s="11" t="n">
-        <v>7.82</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="147">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_create_login_credentials</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="H147" s="11" t="n">
-        <v>11.8</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="148">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_update_pothole_complaint</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr"/>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="H148" s="11" t="n">
-        <v>4.5</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="149">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>test_delete_image_upload</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="H149" s="11" t="n">
-        <v>11.79</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="150">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_submit_street_light_issue</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="H150" s="11" t="n">
-        <v>7.68</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="151">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="H151" s="11" t="n">
-        <v>5.03</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="152">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>test_create_pothole_complaint</t>
+          <t>test_verify_user_profile</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="H152" s="11" t="n">
-        <v>10.72</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="153">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>test_submit_gps_location</t>
+          <t>test_refresh_resolution_status</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr"/>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="H153" s="11" t="n">
-        <v>5.45</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="154">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_resolution_status</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="H154" s="11" t="n">
-        <v>3.06</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>test_delete_street_light_issue</t>
+          <t>test_refresh_resolution_status</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr"/>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="H155" s="11" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="156">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_validate_pothole_complaint</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="H156" s="11" t="n">
-        <v>8.5</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="157">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>test_verify_admin_dashboard</t>
+          <t>test_submit_resolution_status</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr"/>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="H157" s="11" t="n">
-        <v>4.31</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="158">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_submit_resolution_status</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr"/>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="H158" s="11" t="n">
-        <v>2.73</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="H159" s="11" t="n">
-        <v>8.08</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="160">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_submit_gps_location</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr"/>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H160" s="11" t="n">
-        <v>11.18</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="161">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr"/>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="H161" s="11" t="n">
-        <v>7.84</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="162">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>test_delete_user_profile</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr"/>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="H162" s="11" t="n">
-        <v>4.19</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="163">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_resolution_status</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr"/>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="H163" s="11" t="n">
-        <v>9.609999999999999</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="164">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr"/>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="H164" s="11" t="n">
-        <v>6.13</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="165">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_update_street_light_issue</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr"/>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="H165" s="11" t="n">
-        <v>7.87</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="166">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>test_update_gps_location</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr"/>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="H166" s="11" t="n">
-        <v>3.37</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="167">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>test_delete_image_upload</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr"/>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="H167" s="11" t="n">
-        <v>10.48</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="168">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="H168" s="11" t="n">
-        <v>10.47</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="169">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr"/>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="H169" s="11" t="n">
-        <v>9.65</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="170">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>test_create_image_upload</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr"/>
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="H170" s="11" t="n">
-        <v>2.82</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="171">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>test_update_gps_location</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr"/>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="H171" s="11" t="n">
-        <v>10.36</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>test_delete_pothole_complaint</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr"/>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="H172" s="11" t="n">
-        <v>9.640000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="173">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_delete_user_profile</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="H173" s="11" t="n">
-        <v>12.24</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="174">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>test_verify_gps_location</t>
+          <t>test_submit_image_upload</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr"/>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="H174" s="11" t="n">
-        <v>12.29</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="175">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_submit_resolution_status</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="H175" s="11" t="n">
-        <v>9.74</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="176">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="H176" s="11" t="n">
-        <v>7.75</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>test_delete_user_profile</t>
+          <t>test_refresh_image_upload</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="H177" s="11" t="n">
-        <v>3.64</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="178">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_resolution_status</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr"/>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="H178" s="11" t="n">
-        <v>5.05</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="179">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>test_delete_admin_dashboard</t>
+          <t>test_refresh_gps_location</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="H179" s="11" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="180">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_submit_street_light_issue</t>
         </is>
       </c>
       <c r="E180" s="12" t="inlineStr"/>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="H180" s="11" t="n">
-        <v>7.86</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>test_verify_resolution_status</t>
+          <t>test_refresh_user_profile</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="H181" s="11" t="n">
-        <v>5.89</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="182">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_validate_user_profile</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr"/>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="H182" s="11" t="n">
-        <v>8.48</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D183" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_update_pothole_complaint</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="H183" s="11" t="n">
-        <v>5.3</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="184">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_verify_admin_dashboard</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr"/>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="H184" s="11" t="n">
-        <v>3.85</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="185">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>test_validate_street_light_issue</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="H185" s="11" t="n">
-        <v>6.88</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="186">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr"/>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="H186" s="11" t="n">
-        <v>11.79</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="187">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>test_submit_admin_dashboard</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="H187" s="11" t="n">
-        <v>7.93</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="188">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_admin_dashboard</t>
+          <t>test_create_login_credentials</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr"/>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="H188" s="11" t="n">
-        <v>8.27</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="189">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="H189" s="11" t="n">
-        <v>10.7</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="190">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>test_update_admin_dashboard</t>
+          <t>test_verify_password_reset</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr"/>
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="H190" s="11" t="n">
-        <v>5.35</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="191">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>test_submit_admin_dashboard</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="H191" s="11" t="n">
-        <v>7.03</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="192">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>test_delete_login_credentials</t>
+          <t>test_refresh_user_profile</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr"/>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="H192" s="11" t="n">
-        <v>11.17</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="193">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_validate_pothole_complaint</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H193" s="11" t="n">
-        <v>2.92</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="194">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>test_submit_street_light_issue</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="H194" s="11" t="n">
-        <v>3.6</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="195">
@@ -6367,12 +6367,12 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr"/>
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="H195" s="11" t="n">
-        <v>7.47</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="196">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>test_verify_image_upload</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="H196" s="11" t="n">
-        <v>6.58</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D197" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_submit_image_upload</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="H197" s="11" t="n">
-        <v>10.72</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="198">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>test_create_image_upload</t>
+          <t>test_delete_login_credentials</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="H198" s="11" t="n">
-        <v>8.869999999999999</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="199">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E199" s="12" t="inlineStr"/>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="H199" s="11" t="n">
-        <v>10.31</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="200">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>test_validate_street_light_issue</t>
+          <t>test_update_password_reset</t>
         </is>
       </c>
       <c r="E200" s="12" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="H200" s="11" t="n">
-        <v>6.88</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="201">
@@ -6553,12 +6553,12 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D201" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_create_pothole_complaint</t>
         </is>
       </c>
       <c r="E201" s="12" t="inlineStr"/>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="H201" s="11" t="n">
-        <v>10.98</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="202">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D202" s="11" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="H202" s="11" t="n">
-        <v>4.9</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="203">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E203" s="12" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="H203" s="11" t="n">
-        <v>7.43</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>test_update_resolution_status</t>
+          <t>test_create_pothole_complaint</t>
         </is>
       </c>
       <c r="E204" s="12" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="H204" s="11" t="n">
-        <v>9.93</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="205">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E205" s="12" t="inlineStr"/>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="H205" s="11" t="n">
-        <v>6.88</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="206">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D206" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_refresh_password_reset</t>
         </is>
       </c>
       <c r="E206" s="12" t="inlineStr"/>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="H206" s="11" t="n">
-        <v>5.93</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="207">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D207" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_user_profile</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E207" s="12" t="inlineStr"/>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="H207" s="11" t="n">
-        <v>4.48</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="208">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D208" s="11" t="inlineStr">
         <is>
-          <t>test_delete_admin_dashboard</t>
+          <t>test_submit_pothole_complaint</t>
         </is>
       </c>
       <c r="E208" s="12" t="inlineStr"/>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="H208" s="11" t="n">
-        <v>6.59</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="209">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D209" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_delete_login_credentials</t>
         </is>
       </c>
       <c r="E209" s="12" t="inlineStr"/>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="H209" s="11" t="n">
-        <v>10.78</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="210">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D210" s="11" t="inlineStr">
         <is>
-          <t>test_update_password_reset</t>
+          <t>test_delete_password_reset</t>
         </is>
       </c>
       <c r="E210" s="12" t="inlineStr"/>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="H210" s="11" t="n">
-        <v>4.39</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>test_verify_resolution_status</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E211" s="12" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="H211" s="11" t="n">
-        <v>7.6</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D212" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_verify_admin_dashboard</t>
         </is>
       </c>
       <c r="E212" s="12" t="inlineStr"/>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="H212" s="11" t="n">
-        <v>7.68</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="213">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E213" s="12" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="H213" s="11" t="n">
-        <v>4.62</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="214">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D214" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_admin_dashboard</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E214" s="12" t="inlineStr"/>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="H214" s="11" t="n">
-        <v>11.56</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="215">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D215" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E215" s="12" t="inlineStr"/>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="H215" s="11" t="n">
-        <v>4.18</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="216">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D216" s="11" t="inlineStr">
         <is>
-          <t>test_verify_password_reset</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E216" s="12" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="H216" s="11" t="n">
-        <v>3.81</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="217">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D217" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_update_street_light_issue</t>
         </is>
       </c>
       <c r="E217" s="12" t="inlineStr"/>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="H217" s="11" t="n">
-        <v>10.08</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="218">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D218" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_submit_pothole_complaint</t>
         </is>
       </c>
       <c r="E218" s="12" t="inlineStr"/>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="H218" s="11" t="n">
-        <v>11.82</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="219">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>test_submit_street_light_issue</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E219" s="12" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="H219" s="11" t="n">
-        <v>6.14</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="220">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D220" s="11" t="inlineStr">
         <is>
-          <t>test_delete_login_credentials</t>
+          <t>test_validate_admin_dashboard</t>
         </is>
       </c>
       <c r="E220" s="12" t="inlineStr"/>
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="H220" s="11" t="n">
-        <v>8.32</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="221">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D221" s="11" t="inlineStr">
         <is>
-          <t>test_validate_admin_dashboard</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E221" s="12" t="inlineStr"/>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="H221" s="11" t="n">
-        <v>7.97</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="222">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D222" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E222" s="12" t="inlineStr"/>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="H222" s="11" t="n">
-        <v>5.32</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="223">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D223" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E223" s="12" t="inlineStr"/>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="H223" s="11" t="n">
-        <v>8.859999999999999</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="224">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D224" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E224" s="12" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="H224" s="11" t="n">
-        <v>4.34</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="225">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D225" s="11" t="inlineStr">
         <is>
-          <t>test_delete_street_light_issue</t>
+          <t>test_verify_pothole_complaint</t>
         </is>
       </c>
       <c r="E225" s="12" t="inlineStr"/>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="H225" s="11" t="n">
-        <v>10.51</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="226">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D226" s="11" t="inlineStr">
         <is>
-          <t>test_update_admin_dashboard</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E226" s="12" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H226" s="11" t="n">
-        <v>9.67</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="227">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D227" s="11" t="inlineStr">
         <is>
-          <t>test_verify_pothole_complaint</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E227" s="12" t="inlineStr"/>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="H227" s="11" t="n">
-        <v>12.06</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="228">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D228" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E228" s="12" t="inlineStr"/>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="H228" s="11" t="n">
-        <v>11.15</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="229">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D229" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E229" s="12" t="inlineStr"/>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="H229" s="11" t="n">
-        <v>7.36</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="230">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D230" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_delete_admin_dashboard</t>
         </is>
       </c>
       <c r="E230" s="12" t="inlineStr"/>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="H230" s="11" t="n">
-        <v>7.48</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="231">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D231" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_create_user_profile</t>
         </is>
       </c>
       <c r="E231" s="12" t="inlineStr"/>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="H231" s="11" t="n">
-        <v>10.83</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="232">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D232" s="11" t="inlineStr">
         <is>
-          <t>test_update_login_credentials</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E232" s="12" t="inlineStr"/>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="H232" s="11" t="n">
-        <v>10.55</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="233">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D233" s="11" t="inlineStr">
         <is>
-          <t>test_delete_pothole_complaint</t>
+          <t>test_submit_password_reset</t>
         </is>
       </c>
       <c r="E233" s="12" t="inlineStr"/>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="H233" s="11" t="n">
-        <v>3.45</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="234">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D234" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E234" s="12" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="H234" s="11" t="n">
-        <v>3.33</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="235">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D235" s="11" t="inlineStr">
         <is>
-          <t>test_verify_password_reset</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E235" s="12" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="H235" s="11" t="n">
-        <v>7.06</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="236">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D236" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E236" s="12" t="inlineStr"/>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="H236" s="11" t="n">
-        <v>9.07</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="237">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D237" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E237" s="12" t="inlineStr"/>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="H237" s="11" t="n">
-        <v>9.48</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="238">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D238" s="11" t="inlineStr">
         <is>
-          <t>test_update_user_profile</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E238" s="12" t="inlineStr"/>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="H238" s="11" t="n">
-        <v>3.23</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="239">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D239" s="11" t="inlineStr">
         <is>
-          <t>test_verify_pothole_complaint</t>
+          <t>test_refresh_resolution_status</t>
         </is>
       </c>
       <c r="E239" s="12" t="inlineStr"/>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="H239" s="11" t="n">
-        <v>2.79</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="240">
@@ -7762,12 +7762,12 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D240" s="11" t="inlineStr">
         <is>
-          <t>test_validate_login_credentials</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E240" s="12" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="H240" s="11" t="n">
-        <v>11.47</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D241" s="11" t="inlineStr">
         <is>
-          <t>test_validate_gps_location</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E241" s="12" t="inlineStr"/>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="H241" s="11" t="n">
-        <v>8.07</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D242" s="11" t="inlineStr">
         <is>
-          <t>test_submit_street_light_issue</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E242" s="12" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="H242" s="11" t="n">
-        <v>11.79</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="243">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D243" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_create_resolution_status</t>
         </is>
       </c>
       <c r="E243" s="12" t="inlineStr"/>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="H243" s="11" t="n">
-        <v>10.99</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="244">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D244" s="11" t="inlineStr">
         <is>
-          <t>test_update_gps_location</t>
+          <t>test_verify_user_profile</t>
         </is>
       </c>
       <c r="E244" s="12" t="inlineStr"/>
@@ -7906,7 +7906,7 @@
         </is>
       </c>
       <c r="H244" s="11" t="n">
-        <v>8.56</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="245">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D245" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E245" s="12" t="inlineStr"/>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="H245" s="11" t="n">
-        <v>9.789999999999999</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D246" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E246" s="12" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="H246" s="11" t="n">
-        <v>7.53</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="247">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D247" s="11" t="inlineStr">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="H247" s="11" t="n">
-        <v>11.24</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="248">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D248" s="11" t="inlineStr">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="H248" s="11" t="n">
-        <v>9.550000000000001</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="249">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D249" s="11" t="inlineStr">
         <is>
-          <t>test_update_admin_dashboard</t>
+          <t>test_update_pothole_complaint</t>
         </is>
       </c>
       <c r="E249" s="12" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="H249" s="11" t="n">
-        <v>4.73</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="250">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D250" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E250" s="12" t="inlineStr"/>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="H250" s="11" t="n">
-        <v>5.53</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="251">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D251" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E251" s="12" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="H251" s="11" t="n">
-        <v>10.77</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="252">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D252" s="11" t="inlineStr">
         <is>
-          <t>test_delete_street_light_issue</t>
+          <t>test_validate_resolution_status</t>
         </is>
       </c>
       <c r="E252" s="12" t="inlineStr"/>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="H252" s="11" t="n">
-        <v>11.37</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="253">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D253" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_password_reset</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E253" s="12" t="inlineStr"/>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="H253" s="11" t="n">
-        <v>7.4</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="254">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D254" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_password_reset</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E254" s="12" t="inlineStr"/>
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="H254" s="11" t="n">
-        <v>10.24</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="255">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D255" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_validate_admin_dashboard</t>
         </is>
       </c>
       <c r="E255" s="12" t="inlineStr"/>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="H255" s="11" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="256">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="D256" s="11" t="inlineStr">
         <is>
-          <t>test_validate_login_credentials</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E256" s="12" t="inlineStr"/>
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="H256" s="11" t="n">
-        <v>12.13</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="257">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D257" s="11" t="inlineStr">
         <is>
-          <t>test_delete_admin_dashboard</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E257" s="12" t="inlineStr"/>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="H257" s="11" t="n">
-        <v>2.65</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="258">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D258" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_submit_pothole_complaint</t>
         </is>
       </c>
       <c r="E258" s="12" t="inlineStr"/>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="H258" s="11" t="n">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="259">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D259" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_password_reset</t>
+          <t>test_submit_resolution_status</t>
         </is>
       </c>
       <c r="E259" s="12" t="inlineStr"/>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H259" s="11" t="n">
-        <v>8.529999999999999</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="260">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D260" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E260" s="12" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="H260" s="11" t="n">
-        <v>12.33</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="261">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D261" s="11" t="inlineStr">
         <is>
-          <t>test_delete_image_upload</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E261" s="12" t="inlineStr"/>
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="H261" s="11" t="n">
-        <v>6.3</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="262">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D262" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_delete_password_reset</t>
         </is>
       </c>
       <c r="E262" s="12" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="H262" s="11" t="n">
-        <v>10.43</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="263">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D263" s="11" t="inlineStr">
         <is>
-          <t>test_update_user_profile</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E263" s="12" t="inlineStr"/>
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="H263" s="11" t="n">
-        <v>4.71</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="264">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D264" s="11" t="inlineStr">
         <is>
-          <t>test_validate_admin_dashboard</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E264" s="12" t="inlineStr"/>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="H264" s="11" t="n">
-        <v>7.28</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="265">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D265" s="11" t="inlineStr">
         <is>
-          <t>test_validate_admin_dashboard</t>
+          <t>test_submit_pothole_complaint</t>
         </is>
       </c>
       <c r="E265" s="12" t="inlineStr"/>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="H265" s="11" t="n">
-        <v>9.24</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="266">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D266" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_refresh_gps_location</t>
         </is>
       </c>
       <c r="E266" s="12" t="inlineStr"/>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="H266" s="11" t="n">
-        <v>10.53</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="267">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="C267" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D267" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_create_gps_location</t>
         </is>
       </c>
       <c r="E267" s="12" t="inlineStr"/>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="H267" s="11" t="n">
-        <v>11.86</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="268">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C268" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D268" s="11" t="inlineStr">
         <is>
-          <t>test_delete_pothole_complaint</t>
+          <t>test_refresh_street_light_issue</t>
         </is>
       </c>
       <c r="E268" s="12" t="inlineStr"/>
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="H268" s="11" t="n">
-        <v>5.69</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="269">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D269" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E269" s="12" t="inlineStr"/>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="H269" s="11" t="n">
-        <v>7.24</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="C270" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D270" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_user_profile</t>
+          <t>test_submit_resolution_status</t>
         </is>
       </c>
       <c r="E270" s="12" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="H270" s="11" t="n">
-        <v>5.58</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="271">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D271" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_refresh_gps_location</t>
         </is>
       </c>
       <c r="E271" s="12" t="inlineStr"/>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="H271" s="11" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="272">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="C272" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D272" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E272" s="12" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="H272" s="11" t="n">
-        <v>6.9</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="273">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="C273" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D273" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_validate_street_light_issue</t>
         </is>
       </c>
       <c r="E273" s="12" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="H273" s="11" t="n">
-        <v>10.08</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="274">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="C274" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D274" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_submit_gps_location</t>
         </is>
       </c>
       <c r="E274" s="12" t="inlineStr"/>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="H274" s="11" t="n">
-        <v>6.08</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="275">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D275" s="11" t="inlineStr">
         <is>
-          <t>test_validate_login_credentials</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E275" s="12" t="inlineStr"/>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="H275" s="11" t="n">
-        <v>7.59</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="276">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D276" s="11" t="inlineStr">
         <is>
-          <t>test_submit_user_profile</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E276" s="12" t="inlineStr"/>
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="H276" s="11" t="n">
-        <v>12.47</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="277">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D277" s="11" t="inlineStr">
         <is>
-          <t>test_delete_admin_dashboard</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E277" s="12" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="H277" s="11" t="n">
-        <v>4.21</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="278">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D278" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_verify_resolution_status</t>
         </is>
       </c>
       <c r="E278" s="12" t="inlineStr"/>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="H278" s="11" t="n">
-        <v>8.19</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="279">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D279" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E279" s="12" t="inlineStr"/>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="H279" s="11" t="n">
-        <v>10.54</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="280">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D280" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_refresh_resolution_status</t>
         </is>
       </c>
       <c r="E280" s="12" t="inlineStr"/>
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="H280" s="11" t="n">
-        <v>11.68</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="281">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_refresh_password_reset</t>
         </is>
       </c>
       <c r="E281" s="12" t="inlineStr"/>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="H281" s="11" t="n">
-        <v>6.19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D282" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E282" s="12" t="inlineStr"/>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="H282" s="11" t="n">
-        <v>2.88</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="283">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D283" s="11" t="inlineStr">
         <is>
-          <t>test_create_pothole_complaint</t>
+          <t>test_update_password_reset</t>
         </is>
       </c>
       <c r="E283" s="12" t="inlineStr"/>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="H283" s="11" t="n">
-        <v>6.52</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="284">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D284" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_create_image_upload</t>
         </is>
       </c>
       <c r="E284" s="12" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="H284" s="11" t="n">
-        <v>9.640000000000001</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="285">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D285" s="11" t="inlineStr">
         <is>
-          <t>test_delete_user_profile</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E285" s="12" t="inlineStr"/>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="H285" s="11" t="n">
-        <v>4.32</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="286">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D286" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_refresh_street_light_issue</t>
         </is>
       </c>
       <c r="E286" s="12" t="inlineStr"/>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="H286" s="11" t="n">
-        <v>9.01</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="287">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D287" s="11" t="inlineStr">
         <is>
-          <t>test_verify_gps_location</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E287" s="12" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="H287" s="11" t="n">
-        <v>10.54</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="288">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D288" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E288" s="12" t="inlineStr"/>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="H288" s="11" t="n">
-        <v>3.8</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="289">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D289" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_verify_admin_dashboard</t>
         </is>
       </c>
       <c r="E289" s="12" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="H289" s="11" t="n">
-        <v>6.76</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="290">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E290" s="12" t="inlineStr"/>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="H290" s="11" t="n">
-        <v>4.92</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="291">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
-          <t>test_update_password_reset</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E291" s="12" t="inlineStr"/>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="H291" s="11" t="n">
-        <v>8.93</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="292">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
-          <t>test_delete_image_upload</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E292" s="12" t="inlineStr"/>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H292" s="11" t="n">
-        <v>11.88</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="293">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D293" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E293" s="12" t="inlineStr"/>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="H293" s="11" t="n">
-        <v>6.04</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="294">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D294" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E294" s="12" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="H294" s="11" t="n">
-        <v>9.470000000000001</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="295">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D295" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E295" s="12" t="inlineStr"/>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="H295" s="11" t="n">
-        <v>9.68</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="296">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D296" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E296" s="12" t="inlineStr"/>
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="H296" s="11" t="n">
-        <v>3.97</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="297">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="D297" s="11" t="inlineStr">
         <is>
-          <t>test_update_admin_dashboard</t>
+          <t>test_delete_user_profile</t>
         </is>
       </c>
       <c r="E297" s="12" t="inlineStr"/>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="H297" s="11" t="n">
-        <v>7.44</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="298">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D298" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E298" s="12" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="H298" s="11" t="n">
-        <v>8.210000000000001</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="299">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D299" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_validate_login_credentials</t>
         </is>
       </c>
       <c r="E299" s="12" t="inlineStr"/>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="H299" s="11" t="n">
-        <v>10.14</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="300">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D300" s="11" t="inlineStr">
         <is>
-          <t>test_verify_password_reset</t>
+          <t>test_update_password_reset</t>
         </is>
       </c>
       <c r="E300" s="12" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
         </is>
       </c>
       <c r="H300" s="11" t="n">
-        <v>5.61</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="301">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D301" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_refresh_user_profile</t>
         </is>
       </c>
       <c r="E301" s="12" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="H301" s="11" t="n">
-        <v>5.86</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="302">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D302" s="11" t="inlineStr">
         <is>
-          <t>test_delete_resolution_status</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E302" s="12" t="inlineStr"/>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="H302" s="11" t="n">
-        <v>10.55</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="303">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D303" s="11" t="inlineStr">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="H303" s="11" t="n">
-        <v>12.39</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="304">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D304" s="11" t="inlineStr">
         <is>
-          <t>test_create_gps_location</t>
+          <t>test_submit_password_reset</t>
         </is>
       </c>
       <c r="E304" s="12" t="inlineStr"/>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="H304" s="11" t="n">
-        <v>7.42</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="305">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D305" s="11" t="inlineStr">
         <is>
-          <t>test_submit_pothole_complaint</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E305" s="12" t="inlineStr"/>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="H305" s="11" t="n">
-        <v>10.26</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="306">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D306" s="11" t="inlineStr">
         <is>
-          <t>test_delete_resolution_status</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E306" s="12" t="inlineStr"/>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="H306" s="11" t="n">
-        <v>8.390000000000001</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="307">
@@ -9839,12 +9839,12 @@
       </c>
       <c r="C307" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D307" s="11" t="inlineStr">
         <is>
-          <t>test_verify_street_light_issue</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E307" s="12" t="inlineStr"/>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="H307" s="11" t="n">
-        <v>11.26</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="308">
@@ -9870,12 +9870,12 @@
       </c>
       <c r="C308" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D308" s="11" t="inlineStr">
         <is>
-          <t>test_delete_login_credentials</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E308" s="12" t="inlineStr"/>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="H308" s="11" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="309">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D309" s="11" t="inlineStr">
         <is>
-          <t>test_verify_resolution_status</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E309" s="12" t="inlineStr"/>
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="H309" s="11" t="n">
-        <v>10.98</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="310">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D310" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_validate_pothole_complaint</t>
         </is>
       </c>
       <c r="E310" s="12" t="inlineStr"/>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="H310" s="11" t="n">
-        <v>4.91</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="311">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C311" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D311" s="11" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="H311" s="11" t="n">
-        <v>10.01</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="312">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="C312" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D312" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_create_image_upload</t>
         </is>
       </c>
       <c r="E312" s="12" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="H312" s="11" t="n">
-        <v>10.76</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="313">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="C313" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>test_update_user_profile</t>
+          <t>test_create_pothole_complaint</t>
         </is>
       </c>
       <c r="E313" s="12" t="inlineStr"/>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="H313" s="11" t="n">
-        <v>5.43</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="314">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D314" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E314" s="12" t="inlineStr"/>
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="H314" s="11" t="n">
-        <v>6.05</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="315">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D315" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_update_password_reset</t>
         </is>
       </c>
       <c r="E315" s="12" t="inlineStr"/>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="H315" s="11" t="n">
-        <v>5.01</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="316">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="D316" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_gps_location</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E316" s="12" t="inlineStr"/>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="H316" s="11" t="n">
-        <v>5.04</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="317">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="D317" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E317" s="12" t="inlineStr"/>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="H317" s="11" t="n">
-        <v>4.35</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="318">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="C318" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D318" s="11" t="inlineStr">
         <is>
-          <t>test_submit_admin_dashboard</t>
+          <t>test_submit_street_light_issue</t>
         </is>
       </c>
       <c r="E318" s="12" t="inlineStr"/>
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="H318" s="11" t="n">
-        <v>3</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="319">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D319" s="11" t="inlineStr">
         <is>
-          <t>test_validate_login_credentials</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E319" s="12" t="inlineStr"/>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="H319" s="11" t="n">
-        <v>5.95</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="320">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D320" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_verify_user_profile</t>
         </is>
       </c>
       <c r="E320" s="12" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="H320" s="11" t="n">
-        <v>3.99</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="321">
@@ -10273,12 +10273,12 @@
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D321" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E321" s="12" t="inlineStr"/>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="H321" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="322">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D322" s="11" t="inlineStr">
         <is>
-          <t>test_validate_user_profile</t>
+          <t>test_validate_gps_location</t>
         </is>
       </c>
       <c r="E322" s="12" t="inlineStr"/>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="H322" s="11" t="n">
-        <v>3.97</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="323">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="C323" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D323" s="11" t="inlineStr">
         <is>
-          <t>test_create_gps_location</t>
+          <t>test_delete_image_upload</t>
         </is>
       </c>
       <c r="E323" s="12" t="inlineStr"/>
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="H323" s="11" t="n">
-        <v>7.45</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="324">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="D324" s="11" t="inlineStr">
         <is>
-          <t>test_submit_user_profile</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E324" s="12" t="inlineStr"/>
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="H324" s="11" t="n">
-        <v>5.63</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="325">
@@ -10397,12 +10397,12 @@
       </c>
       <c r="C325" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D325" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_resolution_status</t>
+          <t>test_create_image_upload</t>
         </is>
       </c>
       <c r="E325" s="12" t="inlineStr"/>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H325" s="11" t="n">
-        <v>10.34</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="326">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="D326" s="11" t="inlineStr">
         <is>
-          <t>test_validate_image_upload</t>
+          <t>test_submit_resolution_status</t>
         </is>
       </c>
       <c r="E326" s="12" t="inlineStr"/>
@@ -10448,7 +10448,7 @@
         </is>
       </c>
       <c r="H326" s="11" t="n">
-        <v>10.73</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="327">
@@ -10459,12 +10459,12 @@
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D327" s="11" t="inlineStr">
         <is>
-          <t>test_verify_pothole_complaint</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E327" s="12" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
         </is>
       </c>
       <c r="H327" s="11" t="n">
-        <v>11.86</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="328">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D328" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E328" s="12" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="H328" s="11" t="n">
-        <v>12.08</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="329">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D329" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_validate_street_light_issue</t>
         </is>
       </c>
       <c r="E329" s="12" t="inlineStr"/>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="H329" s="11" t="n">
-        <v>12.24</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="330">
@@ -10552,12 +10552,12 @@
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D330" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_verify_user_profile</t>
         </is>
       </c>
       <c r="E330" s="12" t="inlineStr"/>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="H330" s="11" t="n">
-        <v>11.22</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="331">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D331" s="11" t="inlineStr">
         <is>
-          <t>test_verify_image_upload</t>
+          <t>test_refresh_admin_dashboard</t>
         </is>
       </c>
       <c r="E331" s="12" t="inlineStr"/>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="H331" s="11" t="n">
-        <v>9.57</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="332">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D332" s="11" t="inlineStr">
         <is>
-          <t>test_verify_resolution_status</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E332" s="12" t="inlineStr"/>
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="H332" s="11" t="n">
-        <v>9.16</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="333">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="C333" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D333" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_create_image_upload</t>
         </is>
       </c>
       <c r="E333" s="12" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="H333" s="11" t="n">
-        <v>4.75</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="334">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="C334" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D334" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E334" s="12" t="inlineStr"/>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="H334" s="11" t="n">
-        <v>9.18</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="335">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
         <is>
-          <t>test_delete_resolution_status</t>
+          <t>test_submit_image_upload</t>
         </is>
       </c>
       <c r="E335" s="12" t="inlineStr"/>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="H335" s="11" t="n">
-        <v>3.87</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="336">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="C336" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D336" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E336" s="12" t="inlineStr"/>
@@ -10758,7 +10758,7 @@
         </is>
       </c>
       <c r="H336" s="11" t="n">
-        <v>5</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="337">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="C337" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D337" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_validate_admin_dashboard</t>
         </is>
       </c>
       <c r="E337" s="12" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="H337" s="11" t="n">
-        <v>3.01</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="338">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="D338" s="11" t="inlineStr">
         <is>
-          <t>test_update_user_profile</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E338" s="12" t="inlineStr"/>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="H338" s="11" t="n">
-        <v>4.57</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="339">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="C339" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D339" s="11" t="inlineStr">
         <is>
-          <t>test_verify_password_reset</t>
+          <t>test_verify_admin_dashboard</t>
         </is>
       </c>
       <c r="E339" s="12" t="inlineStr"/>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="H339" s="11" t="n">
-        <v>3.45</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="340">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="C340" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D340" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_gps_location</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E340" s="12" t="inlineStr"/>
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="H340" s="11" t="n">
-        <v>5.31</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="C341" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D341" s="11" t="inlineStr">
         <is>
-          <t>test_submit_password_reset</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E341" s="12" t="inlineStr"/>
@@ -10913,7 +10913,7 @@
         </is>
       </c>
       <c r="H341" s="11" t="n">
-        <v>8.17</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="342">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="C342" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D342" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_verify_password_reset</t>
         </is>
       </c>
       <c r="E342" s="12" t="inlineStr"/>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="H342" s="11" t="n">
-        <v>5.73</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="343">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="C343" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D343" s="11" t="inlineStr">
         <is>
-          <t>test_validate_pothole_complaint</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E343" s="12" t="inlineStr"/>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="H343" s="11" t="n">
-        <v>5.24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="C344" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D344" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_validate_pothole_complaint</t>
         </is>
       </c>
       <c r="E344" s="12" t="inlineStr"/>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="H344" s="11" t="n">
-        <v>12.22</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="345">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="C345" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D345" s="11" t="inlineStr">
         <is>
-          <t>test_submit_pothole_complaint</t>
+          <t>test_refresh_admin_dashboard</t>
         </is>
       </c>
       <c r="E345" s="12" t="inlineStr"/>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="H345" s="11" t="n">
-        <v>7.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="346">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="C346" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D346" s="11" t="inlineStr">
         <is>
-          <t>test_create_admin_dashboard</t>
+          <t>test_refresh_gps_location</t>
         </is>
       </c>
       <c r="E346" s="12" t="inlineStr"/>
@@ -11068,7 +11068,7 @@
         </is>
       </c>
       <c r="H346" s="11" t="n">
-        <v>6.37</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="347">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D347" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E347" s="12" t="inlineStr"/>
@@ -11099,7 +11099,7 @@
         </is>
       </c>
       <c r="H347" s="11" t="n">
-        <v>11.08</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="348">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D348" s="11" t="inlineStr">
         <is>
-          <t>test_update_image_upload</t>
+          <t>test_submit_admin_dashboard</t>
         </is>
       </c>
       <c r="E348" s="12" t="inlineStr"/>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="H348" s="11" t="n">
-        <v>11.53</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="349">
@@ -11141,12 +11141,12 @@
       </c>
       <c r="C349" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D349" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_user_profile</t>
+          <t>test_delete_street_light_issue</t>
         </is>
       </c>
       <c r="E349" s="12" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="H349" s="11" t="n">
-        <v>12.09</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="350">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="D350" s="11" t="inlineStr">
         <is>
-          <t>test_validate_street_light_issue</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E350" s="12" t="inlineStr"/>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="H350" s="11" t="n">
-        <v>4.79</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="351">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D351" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E351" s="12" t="inlineStr"/>
@@ -11223,7 +11223,7 @@
         </is>
       </c>
       <c r="H351" s="11" t="n">
-        <v>5.41</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="352">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D352" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_create_street_light_issue</t>
         </is>
       </c>
       <c r="E352" s="12" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
         </is>
       </c>
       <c r="H352" s="11" t="n">
-        <v>11.08</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="353">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="C353" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D353" s="11" t="inlineStr">
         <is>
-          <t>test_update_street_light_issue</t>
+          <t>test_refresh_login_credentials</t>
         </is>
       </c>
       <c r="E353" s="12" t="inlineStr"/>
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="H353" s="11" t="n">
-        <v>12.21</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="354">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="C354" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D354" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_delete_login_credentials</t>
         </is>
       </c>
       <c r="E354" s="12" t="inlineStr"/>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="H354" s="11" t="n">
-        <v>5.61</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="355">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="C355" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D355" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_verify_gps_location</t>
         </is>
       </c>
       <c r="E355" s="12" t="inlineStr"/>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="H355" s="11" t="n">
-        <v>4.69</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="356">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="C356" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D356" s="11" t="inlineStr">
         <is>
-          <t>test_create_admin_dashboard</t>
+          <t>test_validate_pothole_complaint</t>
         </is>
       </c>
       <c r="E356" s="12" t="inlineStr"/>
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="H356" s="11" t="n">
-        <v>7.99</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="357">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="C357" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D357" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E357" s="12" t="inlineStr"/>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="H357" s="11" t="n">
-        <v>10.28</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="358">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="C358" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D358" s="11" t="inlineStr">
         <is>
-          <t>test_create_login_credentials</t>
+          <t>test_validate_admin_dashboard</t>
         </is>
       </c>
       <c r="E358" s="12" t="inlineStr"/>
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H358" s="11" t="n">
-        <v>12.25</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="359">
@@ -11451,12 +11451,12 @@
       </c>
       <c r="C359" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D359" s="11" t="inlineStr">
         <is>
-          <t>test_validate_password_reset</t>
+          <t>test_update_image_upload</t>
         </is>
       </c>
       <c r="E359" s="12" t="inlineStr"/>
@@ -11471,7 +11471,7 @@
         </is>
       </c>
       <c r="H359" s="11" t="n">
-        <v>8.49</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="360">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="C360" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D360" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E360" s="12" t="inlineStr"/>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="H360" s="11" t="n">
-        <v>2.73</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="361">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="C361" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D361" s="11" t="inlineStr">
         <is>
-          <t>test_delete_image_upload</t>
+          <t>test_update_user_profile</t>
         </is>
       </c>
       <c r="E361" s="12" t="inlineStr"/>
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="H361" s="11" t="n">
-        <v>11.6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="362">
@@ -11544,12 +11544,12 @@
       </c>
       <c r="C362" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D362" s="11" t="inlineStr">
         <is>
-          <t>test_create_password_reset</t>
+          <t>test_validate_image_upload</t>
         </is>
       </c>
       <c r="E362" s="12" t="inlineStr"/>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="H362" s="11" t="n">
-        <v>3.46</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="363">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="C363" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D363" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_validate_street_light_issue</t>
         </is>
       </c>
       <c r="E363" s="12" t="inlineStr"/>
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="H363" s="11" t="n">
-        <v>9.08</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="364">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="C364" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D364" s="11" t="inlineStr">
         <is>
-          <t>test_update_gps_location</t>
+          <t>test_validate_password_reset</t>
         </is>
       </c>
       <c r="E364" s="12" t="inlineStr"/>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="H364" s="11" t="n">
-        <v>6.78</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="365">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="D365" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_gps_location</t>
+          <t>test_validate_user_profile</t>
         </is>
       </c>
       <c r="E365" s="12" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="H365" s="11" t="n">
-        <v>8.76</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="366">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="D366" s="11" t="inlineStr">
         <is>
-          <t>test_update_admin_dashboard</t>
+          <t>test_refresh_password_reset</t>
         </is>
       </c>
       <c r="E366" s="12" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="H366" s="11" t="n">
-        <v>6.52</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="367">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="C367" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D367" s="11" t="inlineStr">
         <is>
-          <t>test_verify_login_credentials</t>
+          <t>test_delete_user_profile</t>
         </is>
       </c>
       <c r="E367" s="12" t="inlineStr"/>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="H367" s="11" t="n">
-        <v>6.4</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="368">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="C368" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D368" s="11" t="inlineStr">
         <is>
-          <t>test_verify_resolution_status</t>
+          <t>test_submit_pothole_complaint</t>
         </is>
       </c>
       <c r="E368" s="12" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="H368" s="11" t="n">
-        <v>2.74</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="369">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="C369" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D369" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_update_login_credentials</t>
         </is>
       </c>
       <c r="E369" s="12" t="inlineStr"/>
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="H369" s="11" t="n">
-        <v>11.66</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="370">
@@ -11792,12 +11792,12 @@
       </c>
       <c r="C370" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D370" s="11" t="inlineStr">
         <is>
-          <t>test_validate_resolution_status</t>
+          <t>test_delete_resolution_status</t>
         </is>
       </c>
       <c r="E370" s="12" t="inlineStr"/>
@@ -11812,7 +11812,7 @@
         </is>
       </c>
       <c r="H370" s="11" t="n">
-        <v>12.26</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="371">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="C371" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D371" s="11" t="inlineStr">
         <is>
-          <t>test_update_login_credentials</t>
+          <t>test_refresh_image_upload</t>
         </is>
       </c>
       <c r="E371" s="12" t="inlineStr"/>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="H371" s="11" t="n">
-        <v>6.04</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="372">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C372" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D372" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_login_credentials</t>
+          <t>test_refresh_image_upload</t>
         </is>
       </c>
       <c r="E372" s="12" t="inlineStr"/>
@@ -11874,7 +11874,7 @@
         </is>
       </c>
       <c r="H372" s="11" t="n">
-        <v>5.83</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="373">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="C373" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D373" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_submit_image_upload</t>
         </is>
       </c>
       <c r="E373" s="12" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="H373" s="11" t="n">
-        <v>10.53</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="374">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D374" s="11" t="inlineStr">
         <is>
-          <t>test_verify_image_upload</t>
+          <t>test_submit_password_reset</t>
         </is>
       </c>
       <c r="E374" s="12" t="inlineStr"/>
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="H374" s="11" t="n">
-        <v>4.13</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="375">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="C375" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D375" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E375" s="12" t="inlineStr"/>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="H375" s="11" t="n">
-        <v>7.25</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="376">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="D376" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_user_profile</t>
+          <t>test_delete_login_credentials</t>
         </is>
       </c>
       <c r="E376" s="12" t="inlineStr"/>
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="H376" s="11" t="n">
-        <v>6.4</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="377">
@@ -12009,12 +12009,12 @@
       </c>
       <c r="C377" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D377" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_validate_user_profile</t>
         </is>
       </c>
       <c r="E377" s="12" t="inlineStr"/>
@@ -12029,7 +12029,7 @@
         </is>
       </c>
       <c r="H377" s="11" t="n">
-        <v>10.61</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="378">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="C378" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D378" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E378" s="12" t="inlineStr"/>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="H378" s="11" t="n">
-        <v>4.28</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="379">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="C379" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D379" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E379" s="12" t="inlineStr"/>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="H379" s="11" t="n">
-        <v>4.05</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="C380" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D380" s="11" t="inlineStr">
         <is>
-          <t>test_validate_street_light_issue</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E380" s="12" t="inlineStr"/>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="H380" s="11" t="n">
-        <v>6.32</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="381">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="C381" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D381" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_street_light_issue</t>
+          <t>test_validate_resolution_status</t>
         </is>
       </c>
       <c r="E381" s="12" t="inlineStr"/>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="H381" s="11" t="n">
-        <v>12.29</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="382">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C382" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D382" s="11" t="inlineStr">
         <is>
-          <t>test_verify_admin_dashboard</t>
+          <t>test_submit_password_reset</t>
         </is>
       </c>
       <c r="E382" s="12" t="inlineStr"/>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="H382" s="11" t="n">
-        <v>7.81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="C383" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D383" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_submit_password_reset</t>
         </is>
       </c>
       <c r="E383" s="12" t="inlineStr"/>
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="H383" s="11" t="n">
-        <v>10.47</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="384">
@@ -12226,12 +12226,12 @@
       </c>
       <c r="C384" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D384" s="11" t="inlineStr">
         <is>
-          <t>test_update_admin_dashboard</t>
+          <t>test_submit_image_upload</t>
         </is>
       </c>
       <c r="E384" s="12" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="H384" s="11" t="n">
-        <v>4.55</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="385">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="D385" s="11" t="inlineStr">
         <is>
-          <t>test_create_resolution_status</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E385" s="12" t="inlineStr"/>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="H385" s="11" t="n">
-        <v>8.4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="386">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="C386" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D386" s="11" t="inlineStr">
         <is>
-          <t>test_verify_image_upload</t>
+          <t>test_submit_login_credentials</t>
         </is>
       </c>
       <c r="E386" s="12" t="inlineStr"/>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="H386" s="11" t="n">
-        <v>12.42</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="387">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="C387" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D387" s="11" t="inlineStr">
         <is>
-          <t>test_submit_user_profile</t>
+          <t>test_update_resolution_status</t>
         </is>
       </c>
       <c r="E387" s="12" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
         </is>
       </c>
       <c r="H387" s="11" t="n">
-        <v>10.09</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="388">
@@ -12350,12 +12350,12 @@
       </c>
       <c r="C388" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D388" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E388" s="12" t="inlineStr"/>
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="H388" s="11" t="n">
-        <v>5.69</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="389">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="C389" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D389" s="11" t="inlineStr">
         <is>
-          <t>test_delete_user_profile</t>
+          <t>test_create_user_profile</t>
         </is>
       </c>
       <c r="E389" s="12" t="inlineStr"/>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="H389" s="11" t="n">
-        <v>11.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="390">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="C390" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D390" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_delete_user_profile</t>
         </is>
       </c>
       <c r="E390" s="12" t="inlineStr"/>
@@ -12432,7 +12432,7 @@
         </is>
       </c>
       <c r="H390" s="11" t="n">
-        <v>5.36</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="391">
@@ -12443,12 +12443,12 @@
       </c>
       <c r="C391" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D391" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_refresh_pothole_complaint</t>
         </is>
       </c>
       <c r="E391" s="12" t="inlineStr"/>
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H391" s="11" t="n">
-        <v>7.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="392">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="C392" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D392" s="11" t="inlineStr">
         <is>
-          <t>test_submit_gps_location</t>
+          <t>test_create_password_reset</t>
         </is>
       </c>
       <c r="E392" s="12" t="inlineStr"/>
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="H392" s="11" t="n">
-        <v>9.949999999999999</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="393">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="D393" s="11" t="inlineStr">
         <is>
-          <t>test_verify_user_profile</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E393" s="12" t="inlineStr"/>
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="H393" s="11" t="n">
-        <v>7.43</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="394">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="C394" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="D394" s="11" t="inlineStr">
         <is>
-          <t>test_submit_resolution_status</t>
+          <t>test_validate_street_light_issue</t>
         </is>
       </c>
       <c r="E394" s="12" t="inlineStr"/>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="H394" s="11" t="n">
-        <v>7.19</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="395">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="C395" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D395" s="11" t="inlineStr">
         <is>
-          <t>test_update_password_reset</t>
+          <t>test_refresh_admin_dashboard</t>
         </is>
       </c>
       <c r="E395" s="12" t="inlineStr"/>
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="H395" s="11" t="n">
-        <v>9.82</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="396">
@@ -12598,12 +12598,12 @@
       </c>
       <c r="C396" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D396" s="11" t="inlineStr">
         <is>
-          <t>test_create_admin_dashboard</t>
+          <t>test_verify_image_upload</t>
         </is>
       </c>
       <c r="E396" s="12" t="inlineStr"/>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="H396" s="11" t="n">
-        <v>3.3</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="397">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="C397" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D397" s="11" t="inlineStr">
         <is>
-          <t>test_validate_gps_location</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E397" s="12" t="inlineStr"/>
@@ -12649,7 +12649,7 @@
         </is>
       </c>
       <c r="H397" s="11" t="n">
-        <v>4.37</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="398">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="C398" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D398" s="11" t="inlineStr">
         <is>
-          <t>test_update_pothole_complaint</t>
+          <t>test_verify_resolution_status</t>
         </is>
       </c>
       <c r="E398" s="12" t="inlineStr"/>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="H398" s="11" t="n">
-        <v>9.19</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="399">
@@ -12691,12 +12691,12 @@
       </c>
       <c r="C399" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D399" s="11" t="inlineStr">
         <is>
-          <t>test_submit_admin_dashboard</t>
+          <t>test_update_street_light_issue</t>
         </is>
       </c>
       <c r="E399" s="12" t="inlineStr"/>
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="H399" s="11" t="n">
-        <v>12.49</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="400">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="C400" s="11" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D400" s="11" t="inlineStr">
         <is>
-          <t>test_submit_image_upload</t>
+          <t>test_delete_gps_location</t>
         </is>
       </c>
       <c r="E400" s="12" t="inlineStr"/>
@@ -12742,7 +12742,7 @@
         </is>
       </c>
       <c r="H400" s="11" t="n">
-        <v>9.69</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="401">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="C401" s="11" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D401" s="11" t="inlineStr">
         <is>
-          <t>test_submit_gps_location</t>
+          <t>test_verify_password_reset</t>
         </is>
       </c>
       <c r="E401" s="12" t="inlineStr"/>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="H401" s="11" t="n">
-        <v>3.66</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="402">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="D402" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_image_upload</t>
+          <t>test_update_gps_location</t>
         </is>
       </c>
       <c r="E402" s="12" t="inlineStr"/>
@@ -12804,7 +12804,7 @@
         </is>
       </c>
       <c r="H402" s="11" t="n">
-        <v>9.960000000000001</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="403">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="C403" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D403" s="11" t="inlineStr">
         <is>
-          <t>test_delete_image_upload</t>
+          <t>test_create_admin_dashboard</t>
         </is>
       </c>
       <c r="E403" s="12" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="H403" s="11" t="n">
-        <v>10.21</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="404">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="C404" s="11" t="inlineStr">
         <is>
-          <t>Complaint Creation</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D404" s="11" t="inlineStr">
         <is>
-          <t>test_delete_gps_location</t>
+          <t>test_update_admin_dashboard</t>
         </is>
       </c>
       <c r="E404" s="12" t="inlineStr"/>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="H404" s="11" t="n">
-        <v>12.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="405">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="C405" s="11" t="inlineStr">
         <is>
-          <t>Issue Tracking</t>
+          <t>Complaint Creation</t>
         </is>
       </c>
       <c r="D405" s="11" t="inlineStr">
         <is>
-          <t>test_create_user_profile</t>
+          <t>test_verify_login_credentials</t>
         </is>
       </c>
       <c r="E405" s="12" t="inlineStr"/>
@@ -12897,7 +12897,7 @@
         </is>
       </c>
       <c r="H405" s="11" t="n">
-        <v>12.35</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="406">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="C406" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Issue Tracking</t>
         </is>
       </c>
       <c r="D406" s="11" t="inlineStr">
         <is>
-          <t>test_delete_password_reset</t>
+          <t>test_submit_user_profile</t>
         </is>
       </c>
       <c r="E406" s="12" t="inlineStr"/>
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="H406" s="11" t="n">
-        <v>4.13</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="407">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="D407" s="11" t="inlineStr">
         <is>
-          <t>test_create_street_light_issue</t>
+          <t>test_create_pothole_complaint</t>
         </is>
       </c>
       <c r="E407" s="12" t="inlineStr"/>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="H407" s="11" t="n">
-        <v>12.02</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="408">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="C408" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D408" s="11" t="inlineStr">
         <is>
-          <t>test_submit_login_credentials</t>
+          <t>test_verify_street_light_issue</t>
         </is>
       </c>
       <c r="E408" s="12" t="inlineStr"/>
@@ -12990,7 +12990,7 @@
         </is>
       </c>
       <c r="H408" s="11" t="n">
-        <v>7.47</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="409">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="D409" s="11" t="inlineStr">
         <is>
-          <t>test_submit_gps_location</t>
+          <t>test_validate_resolution_status</t>
         </is>
       </c>
       <c r="E409" s="12" t="inlineStr"/>
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="H409" s="11" t="n">
-        <v>7.04</v>
+        <v>10</v>
       </c>
     </row>
     <row r="410">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="C410" s="11" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D410" s="11" t="inlineStr">
         <is>
-          <t>test_delete_street_light_issue</t>
+          <t>test_delete_pothole_complaint</t>
         </is>
       </c>
       <c r="E410" s="12" t="inlineStr"/>
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="H410" s="11" t="n">
-        <v>10.07</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="411">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="C411" s="11" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D411" s="11" t="inlineStr">
         <is>
-          <t>test_refresh_pothole_complaint</t>
+          <t>test_update_street_light_issue</t>
         </is>
       </c>
       <c r="E411" s="12" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
         </is>
       </c>
       <c r="H411" s="11" t="n">
-        <v>3.22</v>
+        <v>9.85</v>
       </c>
     </row>
   </sheetData>
